--- a/Paket_4_Matematika_TKA_SD.xlsx
+++ b/Paket_4_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 4 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Dalam suatu kompetisi cerdas cermat sains, berlaku aturan skor: setiap jawaban benar mendapat nilai 4, salah mendapat nilai -2, dan tidak dijawab mendapat nilai 0. Dari 25 soal yang diberikan, Farhan berhasil menjawab benar 18 soal dan tidak menjawab 3 soal. Berapakah nilai total yang diperoleh Farhan?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  64</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  68</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  72</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Pak Haris memiliki sawah seluas 2,4 hektar. Sebanyak 3/8 bagian ditanami padi, 0,25 bagian ditanami jagung, dan sisanya ditanami kedelai. Luas sawah yang ditanami kedelai adalah....</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  0,6 hektar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  0,8 hektar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  0,9 hektar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  1,0 hektar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Sebuah sepeda motor membutuhkan 3 liter bensin untuk menempuh jarak 135 km. Berapakah liter bensin yang dibutuhkan sepeda motor tersebut untuk menempuh perjalanan sejauh 225 km dengan kondisi jalan yang sama?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  4,5 liter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  5,0 liter</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  5,5 liter</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  6,0 liter</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,37 +592,42 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Tiga buah lonceng di menara dibunyikan secara berkala. Lonceng A berbunyi setiap 12 menit sekali, lonceng B setiap 15 menit sekali, dan lonceng C setiap 20 menit sekali. Ketiga lonceng berbunyi bersamaan pertama kali pukul 06.00 pagi.
+Manakah pernyataan berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Ketiga lonceng akan berbunyi bersamaan setiap 60 menit sekali.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Ketiga lonceng berbunyi bersamaan untuk kedua kalinya pada pukul 07.00.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Dalam rentang waktu pukul 06.00 hingga 09.30, ketiga lonceng berbunyi bersamaan sebanyak 4 kali.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Lonceng B telah berbunyi sebanyak 3 kali saat ketiga lonceng berbunyi bersama untuk kedua kalinya.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,7 +638,11 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,27 +652,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Dua buah persegi memiliki perbandingan panjang sisi 3 : 5. Jika luas persegi yang lebih kecil adalah 81 cm², berapakah luas persegi yang lebih besar?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  150 cm²</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  175 cm²</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  225 cm²</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  250 cm²</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,17 +683,21 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Pak Sholeh pedagang buah membeli 50 kg apel Malang seharga Rp750.000. Seluruh apel tersebut dijual eceran seharga Rp18.000 per kg. Tentukan nilai kebenaran dari pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,7 +728,11 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,27 +742,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Warga RT 05 mengumpulkan bantuan berupa 84 kg beras, 56 kg gula pasir, dan 42 kaleng sarden. Bantuan tersebut akan dibungkus ke dalam sebanyak mungkin paket plastik yang sama persis tanpa ada sisa. Berapa banyak paket yang dapat dibuat?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  7 paket</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  14 paket</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  21 paket</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  28 paket</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,7 +773,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +787,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Kota P dan Kota Q berjarak 180 km. Dari Kota P, mobil sedan melaju menuju Kota Q pada pukul 08.00 dengan kecepatan rata-rata 55 km/jam. Pada saat yang sama, sebuah truk melaju dari Kota Q menuju Kota P melewati jalan yang sama dengan kecepatan rata-rata 35 km/jam. Pada pukul berapakah kedua kendaraan tersebut akan berpapasan di jalan?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  09.30 WIB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  10.00 WIB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  10.30 WIB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  11.00 WIB</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +818,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +832,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Pak Karto memiliki lahan perkebunan seluas 1,5 hektar. Sebanyak 45 are ditanami pohon kelapa, 6.000 m² ditanami pohon kopi, dan sisanya ditanami kakao. Luas lahan yang ditanami kakao adalah....</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  3.500 m²</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  4.000 m²</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  4.500 m²</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  5.000 m²</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +863,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +877,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Sebuah kolam renang memiliki volume 72 m³. Kolam tersebut dikuras menggunakan pompa air dengan debit 400 liter/menit. Berapa jam waktu yang dibutuhkan untuk mengosongkan seluruh air kolam tersebut? (1 m³ = 1.000 liter)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  2,5 jam</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  3,0 jam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  3,5 jam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  4,0 jam</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,37 +908,42 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebuah segitiga siku-siku memiliki panjang sisi siku-siku 12 cm dan 16 cm, serta panjang sisi miringnya 20 cm.
+Manakah pernyataan berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Keliling segitiga siku-siku tersebut adalah 48 cm.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Luas segitiga siku-siku tersebut adalah 96 cm².</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Tinggi segitiga tersebut jika alasnya 12 cm adalah 16 cm.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Segitiga tersebut memiliki 1 sumbu simetri lipat.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,7 +954,11 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,27 +968,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Sebuah kolam ikan berbentuk lingkaran memiliki diameter 14 meter. Di sekeliling luar kolam tersebut dibangun jalan setapak melingkar selebar 3,5 meter. (Jari-jari lingkaran luar menjadi 7 + 3,5 = 10,5 meter). Berapakah luas jalan setapak melingkar tersebut? (Gunakan π = 22/7)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  154 m²</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  192,5 m²</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  346,5 m²</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  400 m²</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,7 +999,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1013,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebuah kardus besar berbentuk balok memiliki ukuran panjang 40 cm, lebar 30 cm, dan tinggi 20 cm. Kardus tersebut akan diisi kubus-kubus mainan kecil berukuran rusuk 5 cm sampai penuh. Berapa banyak kubus kecil yang dapat termuat di dalam kardus tersebut?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  120 buah</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  160 buah</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  192 buah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  200 buah</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1044,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1058,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah tenda kemah berbentuk prisma segitiga memiliki penampang alas segitiga dengan panjang alas 1,6 meter dan tinggi segitiga 1,5 meter. Jika panjang tenda (tinggi prisma) adalah 3 meter, berapakah volume udara di dalam tenda tersebut?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  3,2 m³</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  3,6 m³</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  4,2 m³</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  7,2 m³</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1089,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Tentukan kebenaran dari pernyataan berikut mengenai sifat limas dan kerucut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1134,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1148,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Hasil penjualan telur ayam di sebuah peternakan selama 6 hari berturut-turut adalah: 120 butir, 140 butir, 110 butir, 150 butir, 130 butir, dan 160 butir. Berapakah rata-rata penjualan telur ayam per hari?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  130 butir</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  135 butir</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  138 butir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  140 butir</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1179,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1193,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Data ekstrakurikuler pilihan 40 siswa kelas 6 adalah: Futsal 14 siswa, Tari 6 siswa, Pramuka 12 siswa, dan Lukis 8 siswa. Modus ekstrakurikuler pilihan siswa adalah....</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Tari</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Lukis</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Pramuka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Futsal</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1224,42 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Diagram batang mencatat hasil panen jagung Desa Sukamaju selama 4 tahun berturut-turut: Tahun 2021 (40 ton), 2022 (55 ton), 2023 (50 ton), 2024 (65 ton).
+Manakah kesimpulan berikut yang BENAR?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kenaikan hasil panen tertinggi terjadi antara tahun 2023 ke 2024.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Total hasil panen selama 4 tahun tersebut adalah 210 ton.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Rata-rata hasil panen jagung per tahun adalah 52,5 ton.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Hasil panen tahun 2022 mengalami penurunan dibanding tahun 2021.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1270,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1284,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Catatan suhu tubuh seorang anak yang sakit demam pada pukul 06.00 adalah 38,5°C; pukul 09.00 naik menjadi 39,2°C; pukul 12.00 turun menjadi 38,0°C; dan pukul 15.00 turun menjadi 37,2°C. Penurunan suhu tubuh terbesar terjadi pada rentang waktu....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Pukul 06.00 - 09.00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Pukul 09.00 - 12.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Pukul 12.00 - 15.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pukul 06.00 - 12.00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1315,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Sebuah lantai dipasangi ubin motif berselang-seling. Baris 1 terdapat 5 ubin putih, baris 2 ada 8 ubin, baris 3 ada 11 ubin, baris 4 ada 14 ubin, dan seterusnya. Tentukan nilai kebenaran dari pernyataan berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1360,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
